--- a/docs/files/meta_variables.xlsx
+++ b/docs/files/meta_variables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lina\STATISTIK\Projects\20210525_shfdb4\dm\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28D8D016-3DA0-4609-83A4-CC62D05E4C1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC082D99-BD3A-4620-AB59-C83B35AC7311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="422">
   <si>
     <t>lopnr</t>
   </si>
@@ -1280,6 +1280,12 @@
   </si>
   <si>
     <t>Composite Death/HFH</t>
+  </si>
+  <si>
+    <t>shf_bmiimp_cat</t>
+  </si>
+  <si>
+    <t>BMI (imputed)</t>
   </si>
 </sst>
 </file>
@@ -1646,7 +1652,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E196"/>
+  <dimension ref="A1:E197"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -2716,7 +2722,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>330</v>
+        <v>421</v>
       </c>
       <c r="C95" t="s">
         <v>331</v>
@@ -2811,219 +2817,219 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>103</v>
+        <v>420</v>
       </c>
       <c r="B105" t="s">
-        <v>256</v>
+        <v>421</v>
       </c>
       <c r="C105" t="s">
-        <v>257</v>
+        <v>331</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>316</v>
-      </c>
-      <c r="C106" s="3"/>
+        <v>256</v>
+      </c>
+      <c r="C106" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>404</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="C107" s="3"/>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>314</v>
-      </c>
-      <c r="C108" s="3"/>
+        <v>404</v>
+      </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>309</v>
-      </c>
+        <v>314</v>
+      </c>
+      <c r="C109" s="3"/>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B112" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>335</v>
-      </c>
-      <c r="E113" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B114" t="s">
-        <v>337</v>
+        <v>335</v>
+      </c>
+      <c r="E114" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B116" t="s">
-        <v>339</v>
-      </c>
-      <c r="E116" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B117" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E117" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B118" t="s">
-        <v>343</v>
-      </c>
-      <c r="C118" t="s">
-        <v>344</v>
+        <v>341</v>
+      </c>
+      <c r="E118" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B119" t="s">
-        <v>345</v>
+        <v>343</v>
+      </c>
+      <c r="C119" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>230</v>
-      </c>
-      <c r="C120" t="s">
-        <v>206</v>
-      </c>
-      <c r="E120" t="s">
-        <v>396</v>
+        <v>345</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B121" t="s">
-        <v>346</v>
+        <v>230</v>
       </c>
       <c r="C121" t="s">
         <v>206</v>
       </c>
       <c r="E121" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B122" t="s">
-        <v>224</v>
+        <v>346</v>
+      </c>
+      <c r="C122" t="s">
+        <v>206</v>
       </c>
       <c r="E122" t="s">
-        <v>347</v>
+        <v>397</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B123" t="s">
-        <v>314</v>
+        <v>224</v>
       </c>
       <c r="E123" t="s">
-        <v>398</v>
+        <v>347</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="E124" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B125" t="s">
-        <v>348</v>
+        <v>309</v>
       </c>
       <c r="E125" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B126" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E126" t="s">
         <v>400</v>
@@ -3031,10 +3037,10 @@
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B127" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E127" t="s">
         <v>400</v>
@@ -3042,10 +3048,10 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B128" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E128" t="s">
         <v>400</v>
@@ -3053,10 +3059,10 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B129" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E129" t="s">
         <v>400</v>
@@ -3064,54 +3070,54 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B130" t="s">
-        <v>320</v>
+        <v>352</v>
       </c>
       <c r="E130" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B131" t="s">
-        <v>353</v>
+        <v>320</v>
       </c>
       <c r="E131" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B132" t="s">
-        <v>316</v>
+        <v>353</v>
       </c>
       <c r="E132" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B133" t="s">
-        <v>354</v>
+        <v>316</v>
       </c>
       <c r="E133" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B134" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E134" t="s">
         <v>400</v>
@@ -3119,10 +3125,10 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B135" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E135" t="s">
         <v>400</v>
@@ -3130,10 +3136,10 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B136" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E136" t="s">
         <v>400</v>
@@ -3141,10 +3147,10 @@
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B137" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E137" t="s">
         <v>400</v>
@@ -3152,10 +3158,10 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B138" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E138" t="s">
         <v>400</v>
@@ -3163,10 +3169,10 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E139" t="s">
         <v>400</v>
@@ -3174,10 +3180,10 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B140" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E140" t="s">
         <v>400</v>
@@ -3185,10 +3191,10 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B141" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E141" t="s">
         <v>400</v>
@@ -3196,10 +3202,10 @@
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B142" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E142" t="s">
         <v>400</v>
@@ -3207,10 +3213,10 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B143" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E143" t="s">
         <v>400</v>
@@ -3218,10 +3224,10 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B144" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E144" t="s">
         <v>400</v>
@@ -3229,10 +3235,10 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B145" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E145" t="s">
         <v>400</v>
@@ -3240,10 +3246,10 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B146" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E146" t="s">
         <v>400</v>
@@ -3251,10 +3257,10 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B147" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E147" t="s">
         <v>400</v>
@@ -3262,10 +3268,10 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B148" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E148" t="s">
         <v>400</v>
@@ -3273,10 +3279,10 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B149" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E149" t="s">
         <v>400</v>
@@ -3284,10 +3290,10 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B150" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E150" t="s">
         <v>400</v>
@@ -3295,10 +3301,10 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B151" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E151" t="s">
         <v>400</v>
@@ -3306,10 +3312,10 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>150</v>
-      </c>
-      <c r="C152" t="s">
-        <v>206</v>
+        <v>149</v>
+      </c>
+      <c r="B152" t="s">
+        <v>372</v>
       </c>
       <c r="E152" t="s">
         <v>400</v>
@@ -3317,10 +3323,10 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>151</v>
-      </c>
-      <c r="B153" t="s">
-        <v>373</v>
+        <v>150</v>
+      </c>
+      <c r="C153" t="s">
+        <v>206</v>
       </c>
       <c r="E153" t="s">
         <v>400</v>
@@ -3328,10 +3334,10 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B154" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E154" t="s">
         <v>400</v>
@@ -3339,10 +3345,10 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>153</v>
-      </c>
-      <c r="C155" t="s">
-        <v>206</v>
+        <v>152</v>
+      </c>
+      <c r="B155" t="s">
+        <v>374</v>
       </c>
       <c r="E155" t="s">
         <v>400</v>
@@ -3350,10 +3356,10 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>154</v>
-      </c>
-      <c r="B156" t="s">
-        <v>375</v>
+        <v>153</v>
+      </c>
+      <c r="C156" t="s">
+        <v>206</v>
       </c>
       <c r="E156" t="s">
         <v>400</v>
@@ -3361,10 +3367,10 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>155</v>
-      </c>
-      <c r="C157" t="s">
-        <v>206</v>
+        <v>154</v>
+      </c>
+      <c r="B157" t="s">
+        <v>375</v>
       </c>
       <c r="E157" t="s">
         <v>400</v>
@@ -3372,10 +3378,10 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>156</v>
-      </c>
-      <c r="B158" t="s">
-        <v>376</v>
+        <v>155</v>
+      </c>
+      <c r="C158" t="s">
+        <v>206</v>
       </c>
       <c r="E158" t="s">
         <v>400</v>
@@ -3383,10 +3389,10 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>157</v>
-      </c>
-      <c r="C159" t="s">
-        <v>206</v>
+        <v>156</v>
+      </c>
+      <c r="B159" t="s">
+        <v>376</v>
       </c>
       <c r="E159" t="s">
         <v>400</v>
@@ -3394,10 +3400,10 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>158</v>
-      </c>
-      <c r="B160" t="s">
-        <v>377</v>
+        <v>157</v>
+      </c>
+      <c r="C160" t="s">
+        <v>206</v>
       </c>
       <c r="E160" t="s">
         <v>400</v>
@@ -3405,10 +3411,10 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>159</v>
-      </c>
-      <c r="C161" t="s">
-        <v>206</v>
+        <v>158</v>
+      </c>
+      <c r="B161" t="s">
+        <v>377</v>
       </c>
       <c r="E161" t="s">
         <v>400</v>
@@ -3416,10 +3422,10 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>160</v>
-      </c>
-      <c r="B162" t="s">
-        <v>378</v>
+        <v>159</v>
+      </c>
+      <c r="C162" t="s">
+        <v>206</v>
       </c>
       <c r="E162" t="s">
         <v>400</v>
@@ -3427,10 +3433,10 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>161</v>
-      </c>
-      <c r="C163" t="s">
-        <v>206</v>
+        <v>160</v>
+      </c>
+      <c r="B163" t="s">
+        <v>378</v>
       </c>
       <c r="E163" t="s">
         <v>400</v>
@@ -3438,10 +3444,10 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>162</v>
-      </c>
-      <c r="B164" t="s">
-        <v>379</v>
+        <v>161</v>
+      </c>
+      <c r="C164" t="s">
+        <v>206</v>
       </c>
       <c r="E164" t="s">
         <v>400</v>
@@ -3449,10 +3455,10 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>163</v>
-      </c>
-      <c r="C165" t="s">
-        <v>206</v>
+        <v>162</v>
+      </c>
+      <c r="B165" t="s">
+        <v>379</v>
       </c>
       <c r="E165" t="s">
         <v>400</v>
@@ -3460,10 +3466,10 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>164</v>
-      </c>
-      <c r="B166" t="s">
-        <v>380</v>
+        <v>163</v>
+      </c>
+      <c r="C166" t="s">
+        <v>206</v>
       </c>
       <c r="E166" t="s">
         <v>400</v>
@@ -3471,10 +3477,10 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>165</v>
-      </c>
-      <c r="C167" t="s">
-        <v>206</v>
+        <v>164</v>
+      </c>
+      <c r="B167" t="s">
+        <v>380</v>
       </c>
       <c r="E167" t="s">
         <v>400</v>
@@ -3482,7 +3488,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C168" t="s">
         <v>206</v>
@@ -3493,10 +3499,10 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>167</v>
-      </c>
-      <c r="B169" t="s">
-        <v>381</v>
+        <v>166</v>
+      </c>
+      <c r="C169" t="s">
+        <v>206</v>
       </c>
       <c r="E169" t="s">
         <v>400</v>
@@ -3504,10 +3510,10 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>168</v>
-      </c>
-      <c r="C170" t="s">
-        <v>206</v>
+        <v>167</v>
+      </c>
+      <c r="B170" t="s">
+        <v>381</v>
       </c>
       <c r="E170" t="s">
         <v>400</v>
@@ -3515,10 +3521,10 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>169</v>
-      </c>
-      <c r="B171" t="s">
-        <v>382</v>
+        <v>168</v>
+      </c>
+      <c r="C171" t="s">
+        <v>206</v>
       </c>
       <c r="E171" t="s">
         <v>400</v>
@@ -3526,10 +3532,10 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>170</v>
-      </c>
-      <c r="C172" t="s">
-        <v>206</v>
+        <v>169</v>
+      </c>
+      <c r="B172" t="s">
+        <v>382</v>
       </c>
       <c r="E172" t="s">
         <v>400</v>
@@ -3537,10 +3543,10 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>171</v>
-      </c>
-      <c r="B173" t="s">
-        <v>383</v>
+        <v>170</v>
+      </c>
+      <c r="C173" t="s">
+        <v>206</v>
       </c>
       <c r="E173" t="s">
         <v>400</v>
@@ -3548,10 +3554,10 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>172</v>
-      </c>
-      <c r="C174" t="s">
-        <v>206</v>
+        <v>171</v>
+      </c>
+      <c r="B174" t="s">
+        <v>383</v>
       </c>
       <c r="E174" t="s">
         <v>400</v>
@@ -3559,10 +3565,10 @@
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>173</v>
-      </c>
-      <c r="B175" t="s">
-        <v>384</v>
+        <v>172</v>
+      </c>
+      <c r="C175" t="s">
+        <v>206</v>
       </c>
       <c r="E175" t="s">
         <v>400</v>
@@ -3570,10 +3576,10 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>174</v>
-      </c>
-      <c r="C176" t="s">
-        <v>206</v>
+        <v>173</v>
+      </c>
+      <c r="B176" t="s">
+        <v>384</v>
       </c>
       <c r="E176" t="s">
         <v>400</v>
@@ -3581,10 +3587,10 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>175</v>
-      </c>
-      <c r="B177" t="s">
-        <v>385</v>
+        <v>174</v>
+      </c>
+      <c r="C177" t="s">
+        <v>206</v>
       </c>
       <c r="E177" t="s">
         <v>400</v>
@@ -3592,10 +3598,10 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>176</v>
-      </c>
-      <c r="C178" t="s">
-        <v>206</v>
+        <v>175</v>
+      </c>
+      <c r="B178" t="s">
+        <v>385</v>
       </c>
       <c r="E178" t="s">
         <v>400</v>
@@ -3603,10 +3609,10 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>177</v>
-      </c>
-      <c r="B179" t="s">
-        <v>386</v>
+        <v>176</v>
+      </c>
+      <c r="C179" t="s">
+        <v>206</v>
       </c>
       <c r="E179" t="s">
         <v>400</v>
@@ -3614,10 +3620,10 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>178</v>
-      </c>
-      <c r="C180" t="s">
-        <v>206</v>
+        <v>177</v>
+      </c>
+      <c r="B180" t="s">
+        <v>386</v>
       </c>
       <c r="E180" t="s">
         <v>400</v>
@@ -3625,10 +3631,10 @@
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>179</v>
-      </c>
-      <c r="B181" t="s">
-        <v>387</v>
+        <v>178</v>
+      </c>
+      <c r="C181" t="s">
+        <v>206</v>
       </c>
       <c r="E181" t="s">
         <v>400</v>
@@ -3636,10 +3642,10 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>180</v>
-      </c>
-      <c r="C182" t="s">
-        <v>206</v>
+        <v>179</v>
+      </c>
+      <c r="B182" t="s">
+        <v>387</v>
       </c>
       <c r="E182" t="s">
         <v>400</v>
@@ -3647,10 +3653,10 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>181</v>
-      </c>
-      <c r="B183" t="s">
-        <v>388</v>
+        <v>180</v>
+      </c>
+      <c r="C183" t="s">
+        <v>206</v>
       </c>
       <c r="E183" t="s">
         <v>400</v>
@@ -3658,10 +3664,10 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>182</v>
-      </c>
-      <c r="C184" t="s">
-        <v>206</v>
+        <v>181</v>
+      </c>
+      <c r="B184" t="s">
+        <v>388</v>
       </c>
       <c r="E184" t="s">
         <v>400</v>
@@ -3669,10 +3675,10 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>183</v>
-      </c>
-      <c r="B185" t="s">
-        <v>389</v>
+        <v>182</v>
+      </c>
+      <c r="C185" t="s">
+        <v>206</v>
       </c>
       <c r="E185" t="s">
         <v>400</v>
@@ -3680,10 +3686,10 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>184</v>
-      </c>
-      <c r="C186" t="s">
-        <v>206</v>
+        <v>183</v>
+      </c>
+      <c r="B186" t="s">
+        <v>389</v>
       </c>
       <c r="E186" t="s">
         <v>400</v>
@@ -3691,10 +3697,10 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>185</v>
-      </c>
-      <c r="B187" t="s">
-        <v>390</v>
+        <v>184</v>
+      </c>
+      <c r="C187" t="s">
+        <v>206</v>
       </c>
       <c r="E187" t="s">
         <v>400</v>
@@ -3702,10 +3708,10 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>186</v>
-      </c>
-      <c r="C188" t="s">
-        <v>206</v>
+        <v>185</v>
+      </c>
+      <c r="B188" t="s">
+        <v>390</v>
       </c>
       <c r="E188" t="s">
         <v>400</v>
@@ -3713,10 +3719,10 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>187</v>
-      </c>
-      <c r="B189" t="s">
-        <v>391</v>
+        <v>186</v>
+      </c>
+      <c r="C189" t="s">
+        <v>206</v>
       </c>
       <c r="E189" t="s">
         <v>400</v>
@@ -3724,10 +3730,10 @@
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>188</v>
-      </c>
-      <c r="C190" t="s">
-        <v>206</v>
+        <v>187</v>
+      </c>
+      <c r="B190" t="s">
+        <v>391</v>
       </c>
       <c r="E190" t="s">
         <v>400</v>
@@ -3735,10 +3741,10 @@
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>189</v>
-      </c>
-      <c r="B191" t="s">
-        <v>392</v>
+        <v>188</v>
+      </c>
+      <c r="C191" t="s">
+        <v>206</v>
       </c>
       <c r="E191" t="s">
         <v>400</v>
@@ -3746,10 +3752,10 @@
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B192" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E192" t="s">
         <v>400</v>
@@ -3757,10 +3763,10 @@
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B193" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E193" t="s">
         <v>400</v>
@@ -3768,25 +3774,36 @@
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B194" t="s">
-        <v>418</v>
+        <v>394</v>
+      </c>
+      <c r="E194" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B195" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
+        <v>193</v>
+      </c>
+      <c r="B196" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
         <v>194</v>
       </c>
-      <c r="B196" t="s">
+      <c r="B197" t="s">
         <v>395</v>
       </c>
     </row>

--- a/docs/files/meta_variables.xlsx
+++ b/docs/files/meta_variables.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lina\STATISTIK\Projects\20210525_shfdb4\dm\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC082D99-BD3A-4620-AB59-C83B35AC7311}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D54350-961B-4BB4-8D8C-8FB325E734A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -763,9 +763,6 @@
     <t>beats/min</t>
   </si>
   <si>
-    <t>Hb</t>
-  </si>
-  <si>
     <t>g/L</t>
   </si>
   <si>
@@ -1096,9 +1093,6 @@
     <t>Valvular disease</t>
   </si>
   <si>
-    <t>Renal failure</t>
-  </si>
-  <si>
     <t>Hyperkalemia</t>
   </si>
   <si>
@@ -1123,12 +1117,6 @@
     <t>Depression</t>
   </si>
   <si>
-    <t>Malignant cancer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muscoloskeletal/connective tissue diseases </t>
-  </si>
-  <si>
     <t>Alcohol abuse</t>
   </si>
   <si>
@@ -1171,9 +1159,6 @@
     <t>Pneumonia hospitalization</t>
   </si>
   <si>
-    <t>Renal Failure hospitalization</t>
-  </si>
-  <si>
     <t>Malignant cancer hospitalization</t>
   </si>
   <si>
@@ -1286,6 +1271,21 @@
   </si>
   <si>
     <t>BMI (imputed)</t>
+  </si>
+  <si>
+    <t>Hemoglobin</t>
+  </si>
+  <si>
+    <t>Kidney disease</t>
+  </si>
+  <si>
+    <t>Kidney disease hospitalization</t>
+  </si>
+  <si>
+    <t>Malignant cancer within 3 years</t>
+  </si>
+  <si>
+    <t>Muscoloskeletal/connective tissue diseases within 3 years</t>
   </si>
 </sst>
 </file>
@@ -1737,7 +1737,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="E8" t="s">
         <v>208</v>
@@ -1779,7 +1779,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C11" t="s">
         <v>210</v>
@@ -1894,7 +1894,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1935,7 +1935,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>211</v>
@@ -2012,10 +2012,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
+        <v>417</v>
+      </c>
+      <c r="C33" t="s">
         <v>247</v>
-      </c>
-      <c r="C33" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2023,13 +2023,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>248</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2037,10 +2037,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>251</v>
+      </c>
+      <c r="C35" t="s">
         <v>252</v>
-      </c>
-      <c r="C35" t="s">
-        <v>253</v>
       </c>
       <c r="D35" t="s">
         <v>234</v>
@@ -2051,10 +2051,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>253</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="D36" s="3"/>
     </row>
@@ -2063,10 +2063,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>255</v>
+      </c>
+      <c r="C37" t="s">
         <v>256</v>
-      </c>
-      <c r="C37" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2074,10 +2074,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
+        <v>257</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>258</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>259</v>
       </c>
       <c r="D38" s="3"/>
     </row>
@@ -2086,10 +2086,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,7 +2097,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C40" t="s">
         <v>210</v>
@@ -2111,10 +2111,10 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>261</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>263</v>
       </c>
       <c r="D41" t="s">
         <v>211</v>
@@ -2125,13 +2125,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" t="s">
         <v>264</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>265</v>
-      </c>
-      <c r="D42" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2139,10 +2139,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="D43" t="s">
         <v>267</v>
-      </c>
-      <c r="D43" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2150,7 +2150,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>211</v>
@@ -2161,7 +2161,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>211</v>
@@ -2172,13 +2172,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>298</v>
+      </c>
+      <c r="D46" t="s">
+        <v>282</v>
+      </c>
+      <c r="E46" t="s">
         <v>299</v>
-      </c>
-      <c r="D46" t="s">
-        <v>283</v>
-      </c>
-      <c r="E46" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2186,16 +2186,16 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>300</v>
+      </c>
+      <c r="C47" t="s">
         <v>301</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>282</v>
+      </c>
+      <c r="E47" t="s">
         <v>302</v>
-      </c>
-      <c r="D47" t="s">
-        <v>283</v>
-      </c>
-      <c r="E47" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2203,13 +2203,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="D48" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E48" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2217,7 +2217,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2225,7 +2225,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2233,7 +2233,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D51" t="s">
         <v>234</v>
@@ -2244,7 +2244,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2252,10 +2252,10 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
+        <v>271</v>
+      </c>
+      <c r="C53" t="s">
         <v>272</v>
-      </c>
-      <c r="C53" t="s">
-        <v>273</v>
       </c>
       <c r="D53" t="s">
         <v>234</v>
@@ -2266,7 +2266,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D54" t="s">
         <v>234</v>
@@ -2277,7 +2277,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2285,7 +2285,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D56" t="s">
         <v>211</v>
@@ -2296,13 +2296,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>276</v>
+      </c>
+      <c r="C57" t="s">
+        <v>272</v>
+      </c>
+      <c r="E57" t="s">
         <v>277</v>
-      </c>
-      <c r="C57" t="s">
-        <v>273</v>
-      </c>
-      <c r="E57" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2310,7 +2310,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2318,7 +2318,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2326,13 +2326,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C60" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E60" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2340,10 +2340,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>281</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="E61" s="1"/>
     </row>
@@ -2352,13 +2352,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C62" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E62" s="1"/>
     </row>
@@ -2367,7 +2367,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2375,7 +2375,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2383,7 +2383,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2391,13 +2391,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C66" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="E66" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2405,7 +2405,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2413,10 +2413,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
+        <v>289</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>290</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2424,16 +2424,16 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E69" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,7 +2441,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2449,7 +2449,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2457,10 +2457,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E72" t="s">
         <v>295</v>
-      </c>
-      <c r="E72" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2468,7 +2468,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2476,7 +2476,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2484,10 +2484,10 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D75" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2495,10 +2495,10 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="D76" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2506,13 +2506,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="C77" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D77" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2520,7 +2520,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D78" t="s">
         <v>211</v>
@@ -2531,7 +2531,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2539,13 +2539,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>305</v>
+      </c>
+      <c r="D80" t="s">
         <v>306</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>307</v>
-      </c>
-      <c r="E80" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2553,13 +2553,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
+        <v>308</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" t="s">
         <v>310</v>
-      </c>
-      <c r="E81" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2567,13 +2567,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="E82" t="s">
         <v>312</v>
-      </c>
-      <c r="E82" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2581,13 +2581,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
+        <v>313</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" t="s">
         <v>314</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E83" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2595,13 +2595,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
+        <v>315</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E84" t="s">
         <v>316</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E84" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2609,10 +2609,10 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2620,10 +2620,10 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2631,13 +2631,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
+        <v>319</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E87" t="s">
         <v>320</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E87" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,13 +2645,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
+        <v>321</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E88" t="s">
         <v>322</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E88" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2659,13 +2659,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E89" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2673,10 +2673,10 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
+        <v>324</v>
+      </c>
+      <c r="E90" t="s">
         <v>325</v>
-      </c>
-      <c r="E90" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2684,7 +2684,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2692,7 +2692,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2700,7 +2700,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2708,13 +2708,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
+        <v>329</v>
+      </c>
+      <c r="C94" t="s">
         <v>330</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94" t="s">
         <v>331</v>
-      </c>
-      <c r="E94" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2722,13 +2722,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C95" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E95" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2763,7 +2763,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2779,10 +2779,10 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
+        <v>248</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>249</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2801,7 +2801,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2809,21 +2809,21 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
+        <v>329</v>
+      </c>
+      <c r="C104" t="s">
         <v>330</v>
-      </c>
-      <c r="C104" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B105" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="C105" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2831,10 +2831,10 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
+        <v>255</v>
+      </c>
+      <c r="C106" t="s">
         <v>256</v>
-      </c>
-      <c r="C106" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2842,7 +2842,7 @@
         <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C107" s="3"/>
     </row>
@@ -2851,7 +2851,7 @@
         <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2859,7 +2859,7 @@
         <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C109" s="3"/>
     </row>
@@ -2868,7 +2868,7 @@
         <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2876,7 +2876,7 @@
         <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2884,7 +2884,7 @@
         <v>109</v>
       </c>
       <c r="B112" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2892,7 +2892,7 @@
         <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,10 +2900,10 @@
         <v>111</v>
       </c>
       <c r="B114" t="s">
+        <v>334</v>
+      </c>
+      <c r="E114" t="s">
         <v>335</v>
-      </c>
-      <c r="E114" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2911,7 +2911,7 @@
         <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2919,7 +2919,7 @@
         <v>113</v>
       </c>
       <c r="B116" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2927,10 +2927,10 @@
         <v>114</v>
       </c>
       <c r="B117" t="s">
+        <v>338</v>
+      </c>
+      <c r="E117" t="s">
         <v>339</v>
-      </c>
-      <c r="E117" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -2938,10 +2938,10 @@
         <v>115</v>
       </c>
       <c r="B118" t="s">
+        <v>340</v>
+      </c>
+      <c r="E118" t="s">
         <v>341</v>
-      </c>
-      <c r="E118" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2949,10 +2949,10 @@
         <v>116</v>
       </c>
       <c r="B119" t="s">
+        <v>342</v>
+      </c>
+      <c r="C119" t="s">
         <v>343</v>
-      </c>
-      <c r="C119" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,7 +2960,7 @@
         <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -2974,7 +2974,7 @@
         <v>206</v>
       </c>
       <c r="E121" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -2982,13 +2982,13 @@
         <v>119</v>
       </c>
       <c r="B122" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C122" t="s">
         <v>206</v>
       </c>
       <c r="E122" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -2999,7 +2999,7 @@
         <v>224</v>
       </c>
       <c r="E123" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -3007,10 +3007,10 @@
         <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E124" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -3018,10 +3018,10 @@
         <v>122</v>
       </c>
       <c r="B125" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E125" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -3029,10 +3029,10 @@
         <v>123</v>
       </c>
       <c r="B126" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E126" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -3040,10 +3040,10 @@
         <v>124</v>
       </c>
       <c r="B127" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E127" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -3051,10 +3051,10 @@
         <v>125</v>
       </c>
       <c r="B128" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E128" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -3062,10 +3062,10 @@
         <v>126</v>
       </c>
       <c r="B129" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E129" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -3073,10 +3073,10 @@
         <v>127</v>
       </c>
       <c r="B130" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E130" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -3084,10 +3084,10 @@
         <v>128</v>
       </c>
       <c r="B131" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E131" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -3095,10 +3095,10 @@
         <v>129</v>
       </c>
       <c r="B132" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E132" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -3106,10 +3106,10 @@
         <v>130</v>
       </c>
       <c r="B133" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E133" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -3117,10 +3117,10 @@
         <v>131</v>
       </c>
       <c r="B134" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E134" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -3128,10 +3128,10 @@
         <v>132</v>
       </c>
       <c r="B135" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E135" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -3139,10 +3139,10 @@
         <v>133</v>
       </c>
       <c r="B136" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E136" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -3150,10 +3150,10 @@
         <v>134</v>
       </c>
       <c r="B137" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E137" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -3161,10 +3161,10 @@
         <v>135</v>
       </c>
       <c r="B138" t="s">
-        <v>358</v>
+        <v>418</v>
       </c>
       <c r="E138" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -3172,10 +3172,10 @@
         <v>136</v>
       </c>
       <c r="B139" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E139" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -3183,10 +3183,10 @@
         <v>137</v>
       </c>
       <c r="B140" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E140" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -3194,10 +3194,10 @@
         <v>138</v>
       </c>
       <c r="B141" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="E141" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -3205,10 +3205,10 @@
         <v>139</v>
       </c>
       <c r="B142" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E142" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -3216,10 +3216,10 @@
         <v>140</v>
       </c>
       <c r="B143" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="E143" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -3227,10 +3227,10 @@
         <v>141</v>
       </c>
       <c r="B144" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E144" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
@@ -3238,10 +3238,10 @@
         <v>142</v>
       </c>
       <c r="B145" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E145" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -3249,10 +3249,10 @@
         <v>143</v>
       </c>
       <c r="B146" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E146" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -3260,10 +3260,10 @@
         <v>144</v>
       </c>
       <c r="B147" t="s">
-        <v>367</v>
+        <v>420</v>
       </c>
       <c r="E147" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -3271,10 +3271,10 @@
         <v>145</v>
       </c>
       <c r="B148" t="s">
-        <v>368</v>
+        <v>421</v>
       </c>
       <c r="E148" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -3282,10 +3282,10 @@
         <v>146</v>
       </c>
       <c r="B149" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E149" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -3293,10 +3293,10 @@
         <v>147</v>
       </c>
       <c r="B150" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="E150" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -3304,10 +3304,10 @@
         <v>148</v>
       </c>
       <c r="B151" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E151" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -3315,10 +3315,10 @@
         <v>149</v>
       </c>
       <c r="B152" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E152" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
@@ -3329,7 +3329,7 @@
         <v>206</v>
       </c>
       <c r="E153" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -3337,10 +3337,10 @@
         <v>151</v>
       </c>
       <c r="B154" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E154" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -3348,10 +3348,10 @@
         <v>152</v>
       </c>
       <c r="B155" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="E155" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -3362,7 +3362,7 @@
         <v>206</v>
       </c>
       <c r="E156" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -3370,10 +3370,10 @@
         <v>154</v>
       </c>
       <c r="B157" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E157" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
@@ -3384,7 +3384,7 @@
         <v>206</v>
       </c>
       <c r="E158" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -3392,10 +3392,10 @@
         <v>156</v>
       </c>
       <c r="B159" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E159" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -3406,7 +3406,7 @@
         <v>206</v>
       </c>
       <c r="E160" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
@@ -3414,10 +3414,10 @@
         <v>158</v>
       </c>
       <c r="B161" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="E161" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -3428,7 +3428,7 @@
         <v>206</v>
       </c>
       <c r="E162" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -3436,10 +3436,10 @@
         <v>160</v>
       </c>
       <c r="B163" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E163" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -3450,7 +3450,7 @@
         <v>206</v>
       </c>
       <c r="E164" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -3458,10 +3458,10 @@
         <v>162</v>
       </c>
       <c r="B165" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E165" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -3472,7 +3472,7 @@
         <v>206</v>
       </c>
       <c r="E166" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -3480,10 +3480,10 @@
         <v>164</v>
       </c>
       <c r="B167" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E167" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -3494,7 +3494,7 @@
         <v>206</v>
       </c>
       <c r="E168" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -3505,7 +3505,7 @@
         <v>206</v>
       </c>
       <c r="E169" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -3513,10 +3513,10 @@
         <v>167</v>
       </c>
       <c r="B170" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="E170" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -3527,7 +3527,7 @@
         <v>206</v>
       </c>
       <c r="E171" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -3535,10 +3535,10 @@
         <v>169</v>
       </c>
       <c r="B172" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E172" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -3549,7 +3549,7 @@
         <v>206</v>
       </c>
       <c r="E173" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -3557,10 +3557,10 @@
         <v>171</v>
       </c>
       <c r="B174" t="s">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="E174" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -3571,7 +3571,7 @@
         <v>206</v>
       </c>
       <c r="E175" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -3579,10 +3579,10 @@
         <v>173</v>
       </c>
       <c r="B176" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="E176" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
@@ -3593,7 +3593,7 @@
         <v>206</v>
       </c>
       <c r="E177" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
@@ -3601,10 +3601,10 @@
         <v>175</v>
       </c>
       <c r="B178" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="E178" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
@@ -3615,7 +3615,7 @@
         <v>206</v>
       </c>
       <c r="E179" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
@@ -3623,10 +3623,10 @@
         <v>177</v>
       </c>
       <c r="B180" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="E180" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
@@ -3637,7 +3637,7 @@
         <v>206</v>
       </c>
       <c r="E181" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
@@ -3645,10 +3645,10 @@
         <v>179</v>
       </c>
       <c r="B182" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="E182" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
@@ -3659,7 +3659,7 @@
         <v>206</v>
       </c>
       <c r="E183" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
@@ -3667,10 +3667,10 @@
         <v>181</v>
       </c>
       <c r="B184" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="E184" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
@@ -3681,7 +3681,7 @@
         <v>206</v>
       </c>
       <c r="E185" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
@@ -3689,10 +3689,10 @@
         <v>183</v>
       </c>
       <c r="B186" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="E186" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
@@ -3703,7 +3703,7 @@
         <v>206</v>
       </c>
       <c r="E187" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
@@ -3711,10 +3711,10 @@
         <v>185</v>
       </c>
       <c r="B188" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="E188" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
@@ -3725,7 +3725,7 @@
         <v>206</v>
       </c>
       <c r="E189" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
@@ -3733,10 +3733,10 @@
         <v>187</v>
       </c>
       <c r="B190" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="E190" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
@@ -3747,7 +3747,7 @@
         <v>206</v>
       </c>
       <c r="E191" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
@@ -3755,10 +3755,10 @@
         <v>189</v>
       </c>
       <c r="B192" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="E192" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
@@ -3766,10 +3766,10 @@
         <v>190</v>
       </c>
       <c r="B193" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="E193" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
@@ -3777,10 +3777,10 @@
         <v>191</v>
       </c>
       <c r="B194" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E194" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
@@ -3788,7 +3788,7 @@
         <v>192</v>
       </c>
       <c r="B195" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
@@ -3796,7 +3796,7 @@
         <v>193</v>
       </c>
       <c r="B196" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
@@ -3804,7 +3804,7 @@
         <v>194</v>
       </c>
       <c r="B197" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>

--- a/docs/files/meta_variables.xlsx
+++ b/docs/files/meta_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25629"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lina\STATISTIK\Projects\20210525_shfdb4\dm\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D54350-961B-4BB4-8D8C-8FB325E734A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E66755-0718-4277-807C-2E090504CB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="424">
   <si>
     <t>lopnr</t>
   </si>
@@ -427,9 +427,6 @@
     <t>sos_com_valvular</t>
   </si>
   <si>
-    <t>sos_com_kidney</t>
-  </si>
-  <si>
     <t>sos_com_hyperkalemia</t>
   </si>
   <si>
@@ -535,9 +532,6 @@
     <t>sos_outtime_hosppneumonia</t>
   </si>
   <si>
-    <t>sos_out_hospkidney</t>
-  </si>
-  <si>
     <t>sos_outtime_hospkidney</t>
   </si>
   <si>
@@ -1276,16 +1270,28 @@
     <t>Hemoglobin</t>
   </si>
   <si>
-    <t>Kidney disease</t>
-  </si>
-  <si>
-    <t>Kidney disease hospitalization</t>
-  </si>
-  <si>
     <t>Malignant cancer within 3 years</t>
   </si>
   <si>
     <t>Muscoloskeletal/connective tissue diseases within 3 years</t>
+  </si>
+  <si>
+    <t>sos_com_renal</t>
+  </si>
+  <si>
+    <t>Renal failure</t>
+  </si>
+  <si>
+    <t>Renal failure hospitalization</t>
+  </si>
+  <si>
+    <t>sos_out_hosprenal</t>
+  </si>
+  <si>
+    <t>sos_com_respiratory</t>
+  </si>
+  <si>
+    <t>Pneumonia/Flue/Respiratory infection</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1658,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E197"/>
+  <dimension ref="A1:E198"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1663,19 +1669,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1683,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1691,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1699,7 +1705,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1707,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1718,10 +1724,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1729,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1737,10 +1743,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E8" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1748,16 +1754,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>207</v>
+      </c>
+      <c r="C9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D9" t="s">
         <v>209</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>210</v>
-      </c>
-      <c r="D9" t="s">
-        <v>211</v>
-      </c>
-      <c r="E9" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1765,13 +1771,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1779,16 +1785,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D11" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E11" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1796,13 +1802,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C12" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E12" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1810,7 +1816,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1818,10 +1824,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C14" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1829,10 +1835,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1840,10 +1846,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1851,10 +1857,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E17" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1862,7 +1868,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1870,7 +1876,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1878,7 +1884,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1886,7 +1892,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1894,7 +1900,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1902,13 +1908,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E23" t="s">
         <v>230</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="E23" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1916,10 +1922,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1927,7 +1933,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1935,10 +1941,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1946,10 +1952,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C27" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1957,13 +1963,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C28" t="s">
+        <v>237</v>
+      </c>
+      <c r="E28" t="s">
         <v>238</v>
-      </c>
-      <c r="C28" t="s">
-        <v>239</v>
-      </c>
-      <c r="E28" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1971,10 +1977,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C29" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1982,10 +1988,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1993,7 +1999,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2001,10 +2007,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C32" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2012,10 +2018,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C33" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2023,13 +2029,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>246</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>248</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2037,13 +2043,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C35" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D35" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2051,10 +2057,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D36" s="3"/>
     </row>
@@ -2063,10 +2069,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C37" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2074,10 +2080,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D38" s="3"/>
     </row>
@@ -2086,10 +2092,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2097,13 +2103,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C40" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D40" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2111,13 +2117,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D41" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2125,13 +2131,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>261</v>
+      </c>
+      <c r="C42" t="s">
+        <v>262</v>
+      </c>
+      <c r="D42" t="s">
         <v>263</v>
-      </c>
-      <c r="C42" t="s">
-        <v>264</v>
-      </c>
-      <c r="D42" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2139,10 +2145,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2150,10 +2156,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -2161,10 +2167,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2172,13 +2178,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D46" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E46" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2186,16 +2192,16 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>298</v>
+      </c>
+      <c r="C47" t="s">
+        <v>299</v>
+      </c>
+      <c r="D47" t="s">
+        <v>280</v>
+      </c>
+      <c r="E47" t="s">
         <v>300</v>
-      </c>
-      <c r="C47" t="s">
-        <v>301</v>
-      </c>
-      <c r="D47" t="s">
-        <v>282</v>
-      </c>
-      <c r="E47" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2203,13 +2209,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D48" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E48" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2217,7 +2223,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2225,7 +2231,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2233,10 +2239,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D51" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2244,7 +2250,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2252,13 +2258,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C53" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D53" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2266,10 +2272,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D54" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2277,7 +2283,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2285,10 +2291,10 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D56" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2296,13 +2302,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C57" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E57" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2310,7 +2316,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2318,7 +2324,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2326,13 +2332,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C60" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E60" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2340,10 +2346,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E61" s="1"/>
     </row>
@@ -2352,13 +2358,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C62" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E62" s="1"/>
     </row>
@@ -2367,7 +2373,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2375,7 +2381,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2383,7 +2389,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2391,13 +2397,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C66" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E66" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2405,7 +2411,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2413,10 +2419,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2424,16 +2430,16 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C69" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E69" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2441,7 +2447,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2449,7 +2455,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2457,10 +2463,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E72" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2468,7 +2474,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2476,7 +2482,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2484,10 +2490,10 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D75" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2495,10 +2501,10 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D76" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2506,13 +2512,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
+        <v>407</v>
+      </c>
+      <c r="C77" t="s">
+        <v>270</v>
+      </c>
+      <c r="D77" t="s">
         <v>409</v>
-      </c>
-      <c r="C77" t="s">
-        <v>272</v>
-      </c>
-      <c r="D77" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2520,10 +2526,10 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D78" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2531,7 +2537,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2539,13 +2545,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>303</v>
+      </c>
+      <c r="D80" t="s">
+        <v>304</v>
+      </c>
+      <c r="E80" t="s">
         <v>305</v>
-      </c>
-      <c r="D80" t="s">
-        <v>306</v>
-      </c>
-      <c r="E80" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2553,13 +2559,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
+        <v>306</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E81" t="s">
         <v>308</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E81" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2567,13 +2573,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E82" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2581,13 +2587,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E83" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2595,13 +2601,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E84" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2609,10 +2615,10 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2620,10 +2626,10 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2631,13 +2637,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E87" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,13 +2651,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E88" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2659,13 +2665,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E89" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2673,10 +2679,10 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E90" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2684,7 +2690,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2692,7 +2698,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2700,7 +2706,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2708,13 +2714,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
+        <v>327</v>
+      </c>
+      <c r="C94" t="s">
+        <v>328</v>
+      </c>
+      <c r="E94" t="s">
         <v>329</v>
-      </c>
-      <c r="C94" t="s">
-        <v>330</v>
-      </c>
-      <c r="E94" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2722,13 +2728,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C95" t="s">
+        <v>328</v>
+      </c>
+      <c r="E95" t="s">
         <v>330</v>
-      </c>
-      <c r="E95" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2736,7 +2742,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2744,10 +2750,10 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C97" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2755,7 +2761,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2763,7 +2769,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2771,7 +2777,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2779,10 +2785,10 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2790,10 +2796,10 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C102" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2801,7 +2807,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2809,21 +2815,21 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C104" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B105" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C105" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2831,10 +2837,10 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C106" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2842,7 +2848,7 @@
         <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C107" s="3"/>
     </row>
@@ -2851,7 +2857,7 @@
         <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2859,7 +2865,7 @@
         <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C109" s="3"/>
     </row>
@@ -2868,7 +2874,7 @@
         <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2876,7 +2882,7 @@
         <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2884,7 +2890,7 @@
         <v>109</v>
       </c>
       <c r="B112" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2892,7 +2898,7 @@
         <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2900,10 +2906,10 @@
         <v>111</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E114" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2911,7 +2917,7 @@
         <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2919,7 +2925,7 @@
         <v>113</v>
       </c>
       <c r="B116" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2927,10 +2933,10 @@
         <v>114</v>
       </c>
       <c r="B117" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E117" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -2938,10 +2944,10 @@
         <v>115</v>
       </c>
       <c r="B118" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E118" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2949,10 +2955,10 @@
         <v>116</v>
       </c>
       <c r="B119" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C119" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2960,7 +2966,7 @@
         <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -2968,13 +2974,13 @@
         <v>118</v>
       </c>
       <c r="B121" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C121" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E121" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
@@ -2982,13 +2988,13 @@
         <v>119</v>
       </c>
       <c r="B122" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C122" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E122" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -2996,10 +3002,10 @@
         <v>120</v>
       </c>
       <c r="B123" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E123" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
@@ -3007,10 +3013,10 @@
         <v>121</v>
       </c>
       <c r="B124" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E124" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -3018,10 +3024,10 @@
         <v>122</v>
       </c>
       <c r="B125" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E125" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -3029,10 +3035,10 @@
         <v>123</v>
       </c>
       <c r="B126" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E126" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -3040,10 +3046,10 @@
         <v>124</v>
       </c>
       <c r="B127" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E127" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -3051,10 +3057,10 @@
         <v>125</v>
       </c>
       <c r="B128" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="E128" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -3062,10 +3068,10 @@
         <v>126</v>
       </c>
       <c r="B129" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E129" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -3073,10 +3079,10 @@
         <v>127</v>
       </c>
       <c r="B130" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E130" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -3084,10 +3090,10 @@
         <v>128</v>
       </c>
       <c r="B131" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E131" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
@@ -3095,10 +3101,10 @@
         <v>129</v>
       </c>
       <c r="B132" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E132" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -3106,10 +3112,10 @@
         <v>130</v>
       </c>
       <c r="B133" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E133" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -3117,10 +3123,10 @@
         <v>131</v>
       </c>
       <c r="B134" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E134" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -3128,10 +3134,10 @@
         <v>132</v>
       </c>
       <c r="B135" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E135" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -3139,10 +3145,10 @@
         <v>133</v>
       </c>
       <c r="B136" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="E136" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -3150,661 +3156,672 @@
         <v>134</v>
       </c>
       <c r="B137" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E137" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>135</v>
+        <v>418</v>
       </c>
       <c r="B138" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E138" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B139" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E139" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B140" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E140" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B141" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E141" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B142" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E142" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>140</v>
+        <v>422</v>
       </c>
       <c r="B143" t="s">
-        <v>361</v>
+        <v>423</v>
       </c>
       <c r="E143" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E144" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B145" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E145" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B146" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E146" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B147" t="s">
-        <v>420</v>
+        <v>362</v>
       </c>
       <c r="E147" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B148" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="E148" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B149" t="s">
-        <v>365</v>
+        <v>417</v>
       </c>
       <c r="E149" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B150" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E150" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B151" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E151" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B152" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E152" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>150</v>
-      </c>
-      <c r="C153" t="s">
-        <v>206</v>
+        <v>148</v>
+      </c>
+      <c r="B153" t="s">
+        <v>366</v>
       </c>
       <c r="E153" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>151</v>
-      </c>
-      <c r="B154" t="s">
-        <v>369</v>
+        <v>149</v>
+      </c>
+      <c r="C154" t="s">
+        <v>204</v>
       </c>
       <c r="E154" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B155" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E155" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>153</v>
-      </c>
-      <c r="C156" t="s">
-        <v>206</v>
+        <v>151</v>
+      </c>
+      <c r="B156" t="s">
+        <v>368</v>
       </c>
       <c r="E156" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>154</v>
-      </c>
-      <c r="B157" t="s">
-        <v>371</v>
+        <v>152</v>
+      </c>
+      <c r="C157" t="s">
+        <v>204</v>
       </c>
       <c r="E157" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>155</v>
-      </c>
-      <c r="C158" t="s">
-        <v>206</v>
+        <v>153</v>
+      </c>
+      <c r="B158" t="s">
+        <v>369</v>
       </c>
       <c r="E158" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>156</v>
-      </c>
-      <c r="B159" t="s">
-        <v>372</v>
+        <v>154</v>
+      </c>
+      <c r="C159" t="s">
+        <v>204</v>
       </c>
       <c r="E159" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>157</v>
-      </c>
-      <c r="C160" t="s">
-        <v>206</v>
+        <v>155</v>
+      </c>
+      <c r="B160" t="s">
+        <v>370</v>
       </c>
       <c r="E160" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>158</v>
-      </c>
-      <c r="B161" t="s">
-        <v>373</v>
+        <v>156</v>
+      </c>
+      <c r="C161" t="s">
+        <v>204</v>
       </c>
       <c r="E161" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>159</v>
-      </c>
-      <c r="C162" t="s">
-        <v>206</v>
+        <v>157</v>
+      </c>
+      <c r="B162" t="s">
+        <v>371</v>
       </c>
       <c r="E162" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>160</v>
-      </c>
-      <c r="B163" t="s">
-        <v>374</v>
+        <v>158</v>
+      </c>
+      <c r="C163" t="s">
+        <v>204</v>
       </c>
       <c r="E163" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>161</v>
-      </c>
-      <c r="C164" t="s">
-        <v>206</v>
+        <v>159</v>
+      </c>
+      <c r="B164" t="s">
+        <v>372</v>
       </c>
       <c r="E164" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>162</v>
-      </c>
-      <c r="B165" t="s">
-        <v>375</v>
+        <v>160</v>
+      </c>
+      <c r="C165" t="s">
+        <v>204</v>
       </c>
       <c r="E165" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>163</v>
-      </c>
-      <c r="C166" t="s">
-        <v>206</v>
+        <v>161</v>
+      </c>
+      <c r="B166" t="s">
+        <v>373</v>
       </c>
       <c r="E166" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>164</v>
-      </c>
-      <c r="B167" t="s">
-        <v>376</v>
+        <v>162</v>
+      </c>
+      <c r="C167" t="s">
+        <v>204</v>
       </c>
       <c r="E167" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>165</v>
-      </c>
-      <c r="C168" t="s">
-        <v>206</v>
+        <v>163</v>
+      </c>
+      <c r="B168" t="s">
+        <v>374</v>
       </c>
       <c r="E168" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C169" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E169" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>167</v>
-      </c>
-      <c r="B170" t="s">
-        <v>377</v>
+        <v>165</v>
+      </c>
+      <c r="C170" t="s">
+        <v>204</v>
       </c>
       <c r="E170" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>168</v>
-      </c>
-      <c r="C171" t="s">
-        <v>206</v>
+        <v>166</v>
+      </c>
+      <c r="B171" t="s">
+        <v>375</v>
       </c>
       <c r="E171" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>169</v>
-      </c>
-      <c r="B172" t="s">
-        <v>378</v>
+        <v>167</v>
+      </c>
+      <c r="C172" t="s">
+        <v>204</v>
       </c>
       <c r="E172" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>170</v>
-      </c>
-      <c r="C173" t="s">
-        <v>206</v>
+        <v>168</v>
+      </c>
+      <c r="B173" t="s">
+        <v>376</v>
       </c>
       <c r="E173" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>171</v>
-      </c>
-      <c r="B174" t="s">
-        <v>419</v>
+        <v>169</v>
+      </c>
+      <c r="C174" t="s">
+        <v>204</v>
       </c>
       <c r="E174" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>172</v>
-      </c>
-      <c r="C175" t="s">
-        <v>206</v>
+        <v>421</v>
+      </c>
+      <c r="B175" t="s">
+        <v>420</v>
       </c>
       <c r="E175" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>173</v>
-      </c>
-      <c r="B176" t="s">
-        <v>379</v>
+        <v>170</v>
+      </c>
+      <c r="C176" t="s">
+        <v>204</v>
       </c>
       <c r="E176" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>174</v>
-      </c>
-      <c r="C177" t="s">
-        <v>206</v>
+        <v>171</v>
+      </c>
+      <c r="B177" t="s">
+        <v>377</v>
       </c>
       <c r="E177" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>175</v>
-      </c>
-      <c r="B178" t="s">
-        <v>380</v>
+        <v>172</v>
+      </c>
+      <c r="C178" t="s">
+        <v>204</v>
       </c>
       <c r="E178" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>176</v>
-      </c>
-      <c r="C179" t="s">
-        <v>206</v>
+        <v>173</v>
+      </c>
+      <c r="B179" t="s">
+        <v>378</v>
       </c>
       <c r="E179" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>177</v>
-      </c>
-      <c r="B180" t="s">
-        <v>381</v>
+        <v>174</v>
+      </c>
+      <c r="C180" t="s">
+        <v>204</v>
       </c>
       <c r="E180" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>178</v>
-      </c>
-      <c r="C181" t="s">
-        <v>206</v>
+        <v>175</v>
+      </c>
+      <c r="B181" t="s">
+        <v>379</v>
       </c>
       <c r="E181" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>179</v>
-      </c>
-      <c r="B182" t="s">
-        <v>382</v>
+        <v>176</v>
+      </c>
+      <c r="C182" t="s">
+        <v>204</v>
       </c>
       <c r="E182" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>180</v>
-      </c>
-      <c r="C183" t="s">
-        <v>206</v>
+        <v>177</v>
+      </c>
+      <c r="B183" t="s">
+        <v>380</v>
       </c>
       <c r="E183" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>181</v>
-      </c>
-      <c r="B184" t="s">
-        <v>383</v>
+        <v>178</v>
+      </c>
+      <c r="C184" t="s">
+        <v>204</v>
       </c>
       <c r="E184" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>182</v>
-      </c>
-      <c r="C185" t="s">
-        <v>206</v>
+        <v>179</v>
+      </c>
+      <c r="B185" t="s">
+        <v>381</v>
       </c>
       <c r="E185" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>183</v>
-      </c>
-      <c r="B186" t="s">
-        <v>384</v>
+        <v>180</v>
+      </c>
+      <c r="C186" t="s">
+        <v>204</v>
       </c>
       <c r="E186" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>184</v>
-      </c>
-      <c r="C187" t="s">
-        <v>206</v>
+        <v>181</v>
+      </c>
+      <c r="B187" t="s">
+        <v>382</v>
       </c>
       <c r="E187" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>185</v>
-      </c>
-      <c r="B188" t="s">
-        <v>385</v>
+        <v>182</v>
+      </c>
+      <c r="C188" t="s">
+        <v>204</v>
       </c>
       <c r="E188" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>186</v>
-      </c>
-      <c r="C189" t="s">
-        <v>206</v>
+        <v>183</v>
+      </c>
+      <c r="B189" t="s">
+        <v>383</v>
       </c>
       <c r="E189" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>187</v>
-      </c>
-      <c r="B190" t="s">
-        <v>386</v>
+        <v>184</v>
+      </c>
+      <c r="C190" t="s">
+        <v>204</v>
       </c>
       <c r="E190" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>188</v>
-      </c>
-      <c r="C191" t="s">
-        <v>206</v>
+        <v>185</v>
+      </c>
+      <c r="B191" t="s">
+        <v>384</v>
       </c>
       <c r="E191" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>189</v>
-      </c>
-      <c r="B192" t="s">
-        <v>387</v>
+        <v>186</v>
+      </c>
+      <c r="C192" t="s">
+        <v>204</v>
       </c>
       <c r="E192" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B193" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="E193" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B194" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E194" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B195" t="s">
-        <v>413</v>
+        <v>387</v>
+      </c>
+      <c r="E195" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B196" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B197" t="s">
-        <v>390</v>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>192</v>
+      </c>
+      <c r="B198" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/docs/files/meta_variables.xlsx
+++ b/docs/files/meta_variables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lina\STATISTIK\Projects\20210525_shfdb4\dm\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E66755-0718-4277-807C-2E090504CB30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3E844F-811F-4720-87C2-7B0AD7BA01B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-30" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -379,9 +379,6 @@
     <t>sos_durationhf</t>
   </si>
   <si>
-    <t>sos_prevhosphf</t>
-  </si>
-  <si>
     <t>sos_location</t>
   </si>
   <si>
@@ -1292,6 +1289,9 @@
   </si>
   <si>
     <t>Pneumonia/Flue/Respiratory infection</t>
+  </si>
+  <si>
+    <t>sos_timeprevhosphf</t>
   </si>
 </sst>
 </file>
@@ -1669,19 +1669,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1697,7 +1697,7 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1705,7 +1705,7 @@
         <v>2</v>
       </c>
       <c r="E4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1713,10 +1713,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1724,10 +1724,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" t="s">
         <v>203</v>
-      </c>
-      <c r="C6" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1735,7 +1735,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1743,10 +1743,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E8" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -1754,16 +1754,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>206</v>
+      </c>
+      <c r="C9" t="s">
         <v>207</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>208</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>209</v>
-      </c>
-      <c r="E9" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
@@ -1771,13 +1771,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>206</v>
+      </c>
+      <c r="C10" t="s">
         <v>207</v>
       </c>
-      <c r="C10" t="s">
-        <v>208</v>
-      </c>
       <c r="E10" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -1785,16 +1785,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C11" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D11" t="s">
+        <v>211</v>
+      </c>
+      <c r="E11" t="s">
         <v>212</v>
-      </c>
-      <c r="E11" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
@@ -1802,13 +1802,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" t="s">
         <v>207</v>
       </c>
-      <c r="C12" t="s">
-        <v>208</v>
-      </c>
       <c r="E12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -1816,7 +1816,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
@@ -1824,10 +1824,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
+        <v>214</v>
+      </c>
+      <c r="C14" t="s">
         <v>215</v>
-      </c>
-      <c r="C14" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -1835,10 +1835,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
@@ -1846,10 +1846,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
+        <v>219</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -1857,10 +1857,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
+        <v>221</v>
+      </c>
+      <c r="E17" t="s">
         <v>222</v>
-      </c>
-      <c r="E17" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -1868,7 +1868,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1876,7 +1876,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1884,7 +1884,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1892,7 +1892,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1900,7 +1900,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -1908,13 +1908,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
+        <v>227</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" t="s">
         <v>229</v>
-      </c>
-      <c r="E23" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1922,10 +1922,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
+        <v>230</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1933,7 +1933,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1941,10 +1941,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1952,10 +1952,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
+        <v>233</v>
+      </c>
+      <c r="C27" t="s">
         <v>234</v>
-      </c>
-      <c r="C27" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1963,13 +1963,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" t="s">
         <v>236</v>
       </c>
-      <c r="C28" t="s">
+      <c r="E28" t="s">
         <v>237</v>
-      </c>
-      <c r="E28" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1977,10 +1977,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" t="s">
         <v>239</v>
-      </c>
-      <c r="C29" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1988,10 +1988,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1999,7 +1999,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -2007,10 +2007,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
+        <v>242</v>
+      </c>
+      <c r="C32" t="s">
         <v>243</v>
-      </c>
-      <c r="C32" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
@@ -2018,10 +2018,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C33" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
@@ -2029,13 +2029,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
+        <v>245</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="D34" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -2043,13 +2043,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
+        <v>248</v>
+      </c>
+      <c r="C35" t="s">
         <v>249</v>
       </c>
-      <c r="C35" t="s">
-        <v>250</v>
-      </c>
       <c r="D35" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -2057,10 +2057,10 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
+        <v>250</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="D36" s="3"/>
     </row>
@@ -2069,10 +2069,10 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
+        <v>252</v>
+      </c>
+      <c r="C37" t="s">
         <v>253</v>
-      </c>
-      <c r="C37" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -2080,10 +2080,10 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
+        <v>254</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="D38" s="3"/>
     </row>
@@ -2092,10 +2092,10 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2103,13 +2103,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C40" t="s">
+        <v>207</v>
+      </c>
+      <c r="D40" t="s">
         <v>208</v>
-      </c>
-      <c r="D40" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2117,13 +2117,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
+        <v>258</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>260</v>
-      </c>
       <c r="D41" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -2131,13 +2131,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
+        <v>260</v>
+      </c>
+      <c r="C42" t="s">
         <v>261</v>
       </c>
-      <c r="C42" t="s">
+      <c r="D42" t="s">
         <v>262</v>
-      </c>
-      <c r="D42" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -2145,10 +2145,10 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
+        <v>263</v>
+      </c>
+      <c r="D43" t="s">
         <v>264</v>
-      </c>
-      <c r="D43" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2156,10 +2156,10 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
@@ -2167,10 +2167,10 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -2178,13 +2178,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" t="s">
+        <v>279</v>
+      </c>
+      <c r="E46" t="s">
         <v>296</v>
-      </c>
-      <c r="D46" t="s">
-        <v>280</v>
-      </c>
-      <c r="E46" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
@@ -2192,16 +2192,16 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
+        <v>297</v>
+      </c>
+      <c r="C47" t="s">
         <v>298</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
+        <v>279</v>
+      </c>
+      <c r="E47" t="s">
         <v>299</v>
-      </c>
-      <c r="D47" t="s">
-        <v>280</v>
-      </c>
-      <c r="E47" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
@@ -2209,13 +2209,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D48" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E48" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -2223,7 +2223,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -2231,7 +2231,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
@@ -2239,10 +2239,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -2250,7 +2250,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -2258,13 +2258,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
+        <v>268</v>
+      </c>
+      <c r="C53" t="s">
         <v>269</v>
       </c>
-      <c r="C53" t="s">
-        <v>270</v>
-      </c>
       <c r="D53" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -2272,10 +2272,10 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D54" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
@@ -2283,7 +2283,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
@@ -2291,10 +2291,10 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D56" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -2302,13 +2302,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
+        <v>273</v>
+      </c>
+      <c r="C57" t="s">
+        <v>269</v>
+      </c>
+      <c r="E57" t="s">
         <v>274</v>
-      </c>
-      <c r="C57" t="s">
-        <v>270</v>
-      </c>
-      <c r="E57" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -2316,7 +2316,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -2324,7 +2324,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2332,13 +2332,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C60" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E60" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2346,10 +2346,10 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
+        <v>278</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="E61" s="1"/>
     </row>
@@ -2358,13 +2358,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C62" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="E62" s="1"/>
     </row>
@@ -2373,7 +2373,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -2381,7 +2381,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2389,7 +2389,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2397,13 +2397,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C66" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E66" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2411,7 +2411,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2419,10 +2419,10 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
+        <v>286</v>
+      </c>
+      <c r="D68" s="5" t="s">
         <v>287</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
@@ -2430,16 +2430,16 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C69" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="E69" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2447,7 +2447,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2455,7 +2455,7 @@
         <v>69</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2463,10 +2463,10 @@
         <v>70</v>
       </c>
       <c r="B72" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="E72" t="s">
         <v>292</v>
-      </c>
-      <c r="E72" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2474,7 +2474,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2482,7 +2482,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2490,10 +2490,10 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D75" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2501,10 +2501,10 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
+        <v>407</v>
+      </c>
+      <c r="D76" t="s">
         <v>408</v>
-      </c>
-      <c r="D76" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
@@ -2512,13 +2512,13 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D77" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2526,10 +2526,10 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D78" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2537,7 +2537,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2545,13 +2545,13 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
+        <v>302</v>
+      </c>
+      <c r="D80" t="s">
         <v>303</v>
       </c>
-      <c r="D80" t="s">
+      <c r="E80" t="s">
         <v>304</v>
-      </c>
-      <c r="E80" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2559,13 +2559,13 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
+        <v>305</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="D81" s="2" t="s">
+      <c r="E81" t="s">
         <v>307</v>
-      </c>
-      <c r="E81" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2573,13 +2573,13 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="E82" t="s">
         <v>309</v>
-      </c>
-      <c r="E82" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2587,13 +2587,13 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
+        <v>310</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E83" t="s">
         <v>311</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E83" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2601,13 +2601,13 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E84" t="s">
         <v>313</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E84" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2615,10 +2615,10 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2626,10 +2626,10 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2637,13 +2637,13 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
+        <v>316</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E87" t="s">
         <v>317</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E87" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2651,13 +2651,13 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
+        <v>318</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E88" t="s">
         <v>319</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E88" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2665,13 +2665,13 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E89" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -2679,10 +2679,10 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
+        <v>321</v>
+      </c>
+      <c r="E90" t="s">
         <v>322</v>
-      </c>
-      <c r="E90" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2690,7 +2690,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2698,7 +2698,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2706,7 +2706,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2714,13 +2714,13 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
+        <v>326</v>
+      </c>
+      <c r="C94" t="s">
         <v>327</v>
       </c>
-      <c r="C94" t="s">
+      <c r="E94" t="s">
         <v>328</v>
-      </c>
-      <c r="E94" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2728,13 +2728,13 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C95" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E95" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2742,7 +2742,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2750,10 +2750,10 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
+        <v>214</v>
+      </c>
+      <c r="C97" t="s">
         <v>215</v>
-      </c>
-      <c r="C97" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2761,7 +2761,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2769,7 +2769,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2777,7 +2777,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2785,10 +2785,10 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
+        <v>245</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2796,10 +2796,10 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
+        <v>242</v>
+      </c>
+      <c r="C102" t="s">
         <v>243</v>
-      </c>
-      <c r="C102" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2807,7 +2807,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2815,21 +2815,21 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
+        <v>326</v>
+      </c>
+      <c r="C104" t="s">
         <v>327</v>
-      </c>
-      <c r="C104" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>412</v>
+      </c>
+      <c r="B105" t="s">
         <v>413</v>
       </c>
-      <c r="B105" t="s">
-        <v>414</v>
-      </c>
       <c r="C105" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
@@ -2837,10 +2837,10 @@
         <v>103</v>
       </c>
       <c r="B106" t="s">
+        <v>252</v>
+      </c>
+      <c r="C106" t="s">
         <v>253</v>
-      </c>
-      <c r="C106" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2848,7 +2848,7 @@
         <v>104</v>
       </c>
       <c r="B107" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C107" s="3"/>
     </row>
@@ -2857,7 +2857,7 @@
         <v>105</v>
       </c>
       <c r="B108" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2865,7 +2865,7 @@
         <v>106</v>
       </c>
       <c r="B109" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C109" s="3"/>
     </row>
@@ -2874,7 +2874,7 @@
         <v>107</v>
       </c>
       <c r="B110" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2882,7 +2882,7 @@
         <v>108</v>
       </c>
       <c r="B111" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2890,7 +2890,7 @@
         <v>109</v>
       </c>
       <c r="B112" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>110</v>
       </c>
       <c r="B113" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2906,10 +2906,10 @@
         <v>111</v>
       </c>
       <c r="B114" t="s">
+        <v>331</v>
+      </c>
+      <c r="E114" t="s">
         <v>332</v>
-      </c>
-      <c r="E114" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2917,7 +2917,7 @@
         <v>112</v>
       </c>
       <c r="B115" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2925,7 +2925,7 @@
         <v>113</v>
       </c>
       <c r="B116" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
@@ -2933,10 +2933,10 @@
         <v>114</v>
       </c>
       <c r="B117" t="s">
+        <v>335</v>
+      </c>
+      <c r="E117" t="s">
         <v>336</v>
-      </c>
-      <c r="E117" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
@@ -2944,10 +2944,10 @@
         <v>115</v>
       </c>
       <c r="B118" t="s">
+        <v>337</v>
+      </c>
+      <c r="E118" t="s">
         <v>338</v>
-      </c>
-      <c r="E118" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -2955,10 +2955,10 @@
         <v>116</v>
       </c>
       <c r="B119" t="s">
+        <v>339</v>
+      </c>
+      <c r="C119" t="s">
         <v>340</v>
-      </c>
-      <c r="C119" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -2966,7 +2966,7 @@
         <v>117</v>
       </c>
       <c r="B120" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
@@ -2974,854 +2974,854 @@
         <v>118</v>
       </c>
       <c r="B121" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C121" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E121" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>119</v>
+        <v>423</v>
       </c>
       <c r="B122" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C122" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E122" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E123" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E124" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E125" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E126" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E127" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E128" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E129" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E130" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E131" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E132" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E133" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E134" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E135" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E136" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B137" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E137" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
+        <v>417</v>
+      </c>
+      <c r="B138" t="s">
         <v>418</v>
       </c>
-      <c r="B138" t="s">
-        <v>419</v>
-      </c>
       <c r="E138" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B139" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E139" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B140" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E140" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E141" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B142" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E142" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>421</v>
+      </c>
+      <c r="B143" t="s">
         <v>422</v>
       </c>
-      <c r="B143" t="s">
-        <v>423</v>
-      </c>
       <c r="E143" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B144" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E144" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B145" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E145" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B146" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="E146" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B147" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="E147" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B148" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="E148" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B149" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="E149" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B150" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="E150" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B151" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="E151" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B152" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="E152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B153" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E153" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C154" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E154" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B155" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E155" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B156" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E156" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C157" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E157" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B158" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E158" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C159" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E159" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B160" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E160" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C161" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E161" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B162" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E162" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C163" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E163" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B164" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E164" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C165" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E165" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B166" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E166" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C167" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E167" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B168" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="E168" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C169" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E169" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C170" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E170" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B171" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E171" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C172" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E172" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B173" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E173" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C174" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E174" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B175" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E175" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C176" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E176" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B177" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E177" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C178" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E178" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B179" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E179" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C180" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E180" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B181" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E181" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C182" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E182" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B183" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E183" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C184" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E184" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B185" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="E185" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C186" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E186" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B187" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="E187" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C188" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E188" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B189" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E189" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C190" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E190" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B191" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E191" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C192" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E192" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B193" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E193" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B194" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E194" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B195" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E195" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B196" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B197" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B198" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/docs/files/meta_variables.xlsx
+++ b/docs/files/meta_variables.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25831"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lina\STATISTIK\Projects\20210525_shfdb4\dm\metadata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD3E844F-811F-4720-87C2-7B0AD7BA01B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{354320F7-0195-4A24-95C0-47AEF24AA227}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="440">
   <si>
     <t>lopnr</t>
   </si>
@@ -616,9 +616,6 @@
     <t>Unique patient id</t>
   </si>
   <si>
-    <t>If the post is a case (from SwedeHF) or control</t>
-  </si>
-  <si>
     <t>For internal use. If it is a post registred in the old or new (prior to April 2017) SwedeHF. Most index posts in old SwedeHF were migrated to new SwedeHF (New SHF migrated from old SHF)</t>
   </si>
   <si>
@@ -778,9 +775,6 @@
     <t>µmol/L</t>
   </si>
   <si>
-    <t>eGFR (CKD-EPI 2021)</t>
-  </si>
-  <si>
     <t>mL/min/1.73 m²</t>
   </si>
   <si>
@@ -1114,9 +1108,6 @@
     <t>Severe bleeding</t>
   </si>
   <si>
-    <t>Charlson comorbidity Index</t>
-  </si>
-  <si>
     <t>Heart failure hospitalization</t>
   </si>
   <si>
@@ -1292,6 +1283,63 @@
   </si>
   <si>
     <t>sos_timeprevhosphf</t>
+  </si>
+  <si>
+    <t>Charlson Comorbidity Index</t>
+  </si>
+  <si>
+    <t>If the post is a case (from SwedeHF or NPR) or control</t>
+  </si>
+  <si>
+    <t>ncontrols</t>
+  </si>
+  <si>
+    <t>Number of controls for the case</t>
+  </si>
+  <si>
+    <t>lopnrcase</t>
+  </si>
+  <si>
+    <t>Unique patient id for the case the control goes together with (for cases the same as lopnr)</t>
+  </si>
+  <si>
+    <t>Defined as shf_sex == "Female" &amp; shf_hb &lt; 120 | shf_sex == "Male" &amp; shf_hb &lt; 130</t>
+  </si>
+  <si>
+    <t>eGFR</t>
+  </si>
+  <si>
+    <t>CKD-EPI 2021</t>
+  </si>
+  <si>
+    <t>shf_qol_cat</t>
+  </si>
+  <si>
+    <t>shf_sos_prevhfh1yr</t>
+  </si>
+  <si>
+    <t>Previous HFH &lt; 1 year</t>
+  </si>
+  <si>
+    <t>Either HFH according to NPR or shf_location = "In-patient"</t>
+  </si>
+  <si>
+    <t>Combined from shf_af, shf_ekg, sos_com_af</t>
+  </si>
+  <si>
+    <t>Combined from sos_com_ihd, shf_revasc, sos_com_pci, sos_com_cabg</t>
+  </si>
+  <si>
+    <t>Combined from shf_hypertentions, sos_com_hypertension</t>
+  </si>
+  <si>
+    <t>Combined from shf_diabetes, sos_com_diabetes</t>
+  </si>
+  <si>
+    <t>Combined from shf_valvedisease, sos_com_valvular</t>
+  </si>
+  <si>
+    <t>sos_com_charlsonci_cat</t>
   </si>
 </sst>
 </file>
@@ -1658,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E198"/>
+  <dimension ref="A1:E203"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.140625" customWidth="1"/>
@@ -1697,2131 +1745,2204 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>198</v>
+        <v>422</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>423</v>
       </c>
       <c r="E4" t="s">
-        <v>199</v>
+        <v>424</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>201</v>
+        <v>425</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>202</v>
-      </c>
-      <c r="C6" t="s">
-        <v>203</v>
+        <v>2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>200</v>
+      </c>
+      <c r="E7" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>397</v>
-      </c>
-      <c r="E8" t="s">
-        <v>205</v>
+        <v>201</v>
+      </c>
+      <c r="C8" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>206</v>
-      </c>
-      <c r="C9" t="s">
-        <v>207</v>
-      </c>
-      <c r="D9" t="s">
-        <v>208</v>
-      </c>
-      <c r="E9" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" t="s">
-        <v>207</v>
+        <v>394</v>
       </c>
       <c r="E10" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>398</v>
+        <v>205</v>
       </c>
       <c r="C11" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" t="s">
         <v>207</v>
       </c>
-      <c r="D11" t="s">
-        <v>211</v>
-      </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" t="s">
         <v>206</v>
       </c>
-      <c r="C12" t="s">
-        <v>207</v>
-      </c>
       <c r="E12" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>213</v>
+        <v>395</v>
+      </c>
+      <c r="C13" t="s">
+        <v>206</v>
+      </c>
+      <c r="D13" t="s">
+        <v>210</v>
+      </c>
+      <c r="E13" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C14" t="s">
-        <v>215</v>
+        <v>206</v>
+      </c>
+      <c r="E14" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
+      </c>
+      <c r="C16" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>221</v>
-      </c>
-      <c r="E17" t="s">
-        <v>222</v>
+        <v>213</v>
+      </c>
+      <c r="C17" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>215</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>218</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>225</v>
+        <v>220</v>
+      </c>
+      <c r="E20" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>399</v>
+        <v>223</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>227</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="E23" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B24" t="s">
-        <v>230</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>400</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>208</v>
+        <v>396</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B27" t="s">
-        <v>233</v>
-      </c>
-      <c r="C27" t="s">
-        <v>234</v>
+        <v>226</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E27" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>235</v>
-      </c>
-      <c r="C28" t="s">
-        <v>236</v>
-      </c>
-      <c r="E28" t="s">
-        <v>237</v>
+        <v>229</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B29" t="s">
-        <v>238</v>
-      </c>
-      <c r="C29" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>240</v>
-      </c>
-      <c r="C30" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B31" t="s">
-        <v>241</v>
+        <v>397</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C32" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B33" t="s">
-        <v>414</v>
+        <v>234</v>
       </c>
       <c r="C33" t="s">
-        <v>244</v>
+        <v>235</v>
+      </c>
+      <c r="E33" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>245</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
+      </c>
+      <c r="C34" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="C35" t="s">
-        <v>249</v>
-      </c>
-      <c r="D35" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B36" t="s">
-        <v>250</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D36" s="3"/>
+        <v>240</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="B37" t="s">
-        <v>252</v>
-      </c>
-      <c r="C37" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B38" t="s">
-        <v>254</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="D38" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="C38" t="s">
+        <v>242</v>
+      </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>255</v>
+        <v>241</v>
+      </c>
+      <c r="C39" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B40" t="s">
-        <v>257</v>
+        <v>411</v>
       </c>
       <c r="C40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D40" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="D41" t="s">
-        <v>208</v>
+        <v>392</v>
+      </c>
+      <c r="E41" t="s">
+        <v>427</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B42" t="s">
-        <v>260</v>
-      </c>
-      <c r="C42" t="s">
-        <v>261</v>
-      </c>
-      <c r="D42" t="s">
-        <v>262</v>
+        <v>244</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>99</v>
       </c>
       <c r="B43" t="s">
-        <v>263</v>
-      </c>
-      <c r="D43" t="s">
-        <v>264</v>
+        <v>244</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>401</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>208</v>
+        <v>247</v>
+      </c>
+      <c r="C44" t="s">
+        <v>248</v>
+      </c>
+      <c r="D44" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B45" t="s">
-        <v>402</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>208</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D45" s="3"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="B46" t="s">
-        <v>295</v>
-      </c>
-      <c r="D46" t="s">
-        <v>279</v>
+        <v>428</v>
+      </c>
+      <c r="C46" t="s">
+        <v>251</v>
       </c>
       <c r="E46" t="s">
-        <v>296</v>
+        <v>429</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>297</v>
+        <v>428</v>
       </c>
       <c r="C47" t="s">
-        <v>298</v>
-      </c>
-      <c r="D47" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="E47" t="s">
-        <v>299</v>
+        <v>429</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B48" t="s">
-        <v>403</v>
-      </c>
-      <c r="D48" t="s">
-        <v>279</v>
-      </c>
-      <c r="E48" t="s">
-        <v>300</v>
-      </c>
+        <v>252</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="D48" s="3"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B49" t="s">
-        <v>404</v>
+        <v>254</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>265</v>
+        <v>255</v>
+      </c>
+      <c r="C50" t="s">
+        <v>206</v>
+      </c>
+      <c r="D50" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="B51" t="s">
-        <v>266</v>
+        <v>256</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="D51" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B52" t="s">
-        <v>267</v>
+        <v>258</v>
+      </c>
+      <c r="C52" t="s">
+        <v>259</v>
+      </c>
+      <c r="D52" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B53" t="s">
-        <v>268</v>
-      </c>
-      <c r="C53" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>231</v>
+        <v>262</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B54" t="s">
-        <v>270</v>
-      </c>
-      <c r="D54" t="s">
-        <v>231</v>
+        <v>398</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B55" t="s">
-        <v>271</v>
+        <v>399</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="D56" t="s">
-        <v>208</v>
+        <v>277</v>
+      </c>
+      <c r="E56" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C57" t="s">
-        <v>269</v>
+        <v>296</v>
+      </c>
+      <c r="D57" t="s">
+        <v>277</v>
       </c>
       <c r="E57" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B58" t="s">
-        <v>275</v>
+        <v>400</v>
+      </c>
+      <c r="D58" t="s">
+        <v>277</v>
+      </c>
+      <c r="E58" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="B59" t="s">
-        <v>276</v>
+        <v>401</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="B60" t="s">
-        <v>277</v>
-      </c>
-      <c r="C60" t="s">
-        <v>269</v>
-      </c>
-      <c r="E60" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="B61" t="s">
-        <v>278</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E61" s="1"/>
+        <v>264</v>
+      </c>
+      <c r="D61" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B62" t="s">
-        <v>280</v>
-      </c>
-      <c r="C62" t="s">
-        <v>269</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E62" s="1"/>
+        <v>265</v>
+      </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="B63" t="s">
-        <v>281</v>
+        <v>266</v>
+      </c>
+      <c r="C63" t="s">
+        <v>267</v>
+      </c>
+      <c r="D63" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="B64" t="s">
-        <v>282</v>
+        <v>268</v>
+      </c>
+      <c r="D64" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B65" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>284</v>
-      </c>
-      <c r="C66" t="s">
-        <v>269</v>
-      </c>
-      <c r="E66" t="s">
-        <v>274</v>
+        <v>270</v>
+      </c>
+      <c r="D66" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B67" t="s">
-        <v>285</v>
+        <v>271</v>
+      </c>
+      <c r="C67" t="s">
+        <v>267</v>
+      </c>
+      <c r="E67" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B68" t="s">
-        <v>286</v>
-      </c>
-      <c r="D68" s="5" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B69" t="s">
-        <v>288</v>
-      </c>
-      <c r="C69" t="s">
-        <v>269</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="E69" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B70" t="s">
-        <v>289</v>
+        <v>275</v>
+      </c>
+      <c r="C70" t="s">
+        <v>267</v>
+      </c>
+      <c r="E70" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>290</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B71" t="s">
+        <v>276</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E71" s="1"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E72" t="s">
-        <v>292</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B72" t="s">
+        <v>278</v>
+      </c>
+      <c r="C72" t="s">
+        <v>267</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E72" s="1"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B73" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="B74" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B75" t="s">
-        <v>405</v>
-      </c>
-      <c r="D75" t="s">
-        <v>408</v>
+        <v>281</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B76" t="s">
-        <v>407</v>
-      </c>
-      <c r="D76" t="s">
-        <v>408</v>
+        <v>282</v>
+      </c>
+      <c r="C76" t="s">
+        <v>267</v>
+      </c>
+      <c r="E76" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B77" t="s">
-        <v>406</v>
-      </c>
-      <c r="C77" t="s">
-        <v>269</v>
-      </c>
-      <c r="D77" t="s">
-        <v>408</v>
+        <v>283</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>409</v>
-      </c>
-      <c r="D78" t="s">
-        <v>208</v>
+        <v>284</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B79" t="s">
-        <v>301</v>
+        <v>286</v>
+      </c>
+      <c r="C79" t="s">
+        <v>267</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="E79" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
-        <v>302</v>
-      </c>
-      <c r="D80" t="s">
-        <v>303</v>
-      </c>
-      <c r="E80" t="s">
-        <v>304</v>
+        <v>287</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>79</v>
-      </c>
-      <c r="B81" t="s">
-        <v>305</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E81" t="s">
-        <v>307</v>
+        <v>69</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>80</v>
-      </c>
-      <c r="B82" t="s">
-        <v>305</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>308</v>
+        <v>70</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="E82" t="s">
-        <v>309</v>
+        <v>290</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="B83" t="s">
-        <v>310</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E83" t="s">
-        <v>311</v>
+        <v>291</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="B84" t="s">
-        <v>312</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E84" t="s">
-        <v>313</v>
+        <v>292</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B85" t="s">
-        <v>314</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>306</v>
+        <v>402</v>
+      </c>
+      <c r="D85" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="B86" t="s">
-        <v>315</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>306</v>
+        <v>404</v>
+      </c>
+      <c r="D86" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B87" t="s">
-        <v>316</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E87" t="s">
-        <v>317</v>
+        <v>403</v>
+      </c>
+      <c r="C87" t="s">
+        <v>267</v>
+      </c>
+      <c r="D87" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B88" t="s">
-        <v>318</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E88" t="s">
-        <v>319</v>
+        <v>406</v>
+      </c>
+      <c r="D88" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B89" t="s">
-        <v>320</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E89" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="B90" t="s">
-        <v>321</v>
-      </c>
-      <c r="E90" t="s">
-        <v>322</v>
+        <v>299</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B91" t="s">
-        <v>323</v>
+        <v>300</v>
+      </c>
+      <c r="D91" t="s">
+        <v>301</v>
+      </c>
+      <c r="E91" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B92" t="s">
-        <v>324</v>
+        <v>303</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E92" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B93" t="s">
-        <v>325</v>
+        <v>303</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E93" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B94" t="s">
-        <v>326</v>
-      </c>
-      <c r="C94" t="s">
-        <v>327</v>
+        <v>308</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="E94" t="s">
-        <v>328</v>
+        <v>309</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B95" t="s">
-        <v>413</v>
-      </c>
-      <c r="C95" t="s">
-        <v>327</v>
+        <v>310</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>304</v>
       </c>
       <c r="E95" t="s">
-        <v>329</v>
+        <v>311</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B96" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B97" t="s">
-        <v>214</v>
-      </c>
-      <c r="C97" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B98" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E98" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B99" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+        <v>316</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E99" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B100" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+        <v>318</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E100" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B101" t="s">
-        <v>245</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+        <v>319</v>
+      </c>
+      <c r="E101" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B102" t="s">
-        <v>242</v>
-      </c>
-      <c r="C102" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B103" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>91</v>
+      </c>
+      <c r="B105" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>430</v>
+      </c>
+      <c r="B106" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>92</v>
+      </c>
+      <c r="B107" t="s">
+        <v>324</v>
+      </c>
+      <c r="C107" t="s">
+        <v>325</v>
+      </c>
+      <c r="E107" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>93</v>
+      </c>
+      <c r="B108" t="s">
+        <v>410</v>
+      </c>
+      <c r="C108" t="s">
+        <v>325</v>
+      </c>
+      <c r="E108" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
         <v>102</v>
       </c>
-      <c r="B104" t="s">
-        <v>326</v>
-      </c>
-      <c r="C104" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>412</v>
-      </c>
-      <c r="B105" t="s">
-        <v>413</v>
-      </c>
-      <c r="C105" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>103</v>
-      </c>
-      <c r="B106" t="s">
-        <v>252</v>
-      </c>
-      <c r="C106" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
+      <c r="B109" t="s">
+        <v>324</v>
+      </c>
+      <c r="C109" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>409</v>
+      </c>
+      <c r="B110" t="s">
+        <v>410</v>
+      </c>
+      <c r="C110" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>431</v>
+      </c>
+      <c r="B111" t="s">
+        <v>432</v>
+      </c>
+      <c r="E111" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>104</v>
       </c>
-      <c r="B107" t="s">
-        <v>312</v>
-      </c>
-      <c r="C107" s="3"/>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>105</v>
-      </c>
-      <c r="B108" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>106</v>
-      </c>
-      <c r="B109" t="s">
+      <c r="B112" t="s">
         <v>310</v>
       </c>
-      <c r="C109" s="3"/>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" t="s">
-        <v>107</v>
-      </c>
-      <c r="B110" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>108</v>
-      </c>
-      <c r="B111" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" t="s">
-        <v>109</v>
-      </c>
-      <c r="B112" t="s">
-        <v>324</v>
+      <c r="C112" s="3"/>
+      <c r="E112" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B113" t="s">
-        <v>330</v>
+        <v>393</v>
+      </c>
+      <c r="E113" t="s">
+        <v>435</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B114" t="s">
-        <v>331</v>
-      </c>
+        <v>308</v>
+      </c>
+      <c r="C114" s="3"/>
       <c r="E114" t="s">
-        <v>332</v>
+        <v>436</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B115" t="s">
-        <v>333</v>
+        <v>303</v>
+      </c>
+      <c r="E115" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B116" t="s">
-        <v>334</v>
+        <v>313</v>
+      </c>
+      <c r="E116" t="s">
+        <v>438</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B117" t="s">
-        <v>335</v>
-      </c>
-      <c r="E117" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B118" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E118" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B119" t="s">
-        <v>339</v>
-      </c>
-      <c r="C119" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B120" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B121" t="s">
-        <v>227</v>
-      </c>
-      <c r="C121" t="s">
-        <v>203</v>
+        <v>333</v>
       </c>
       <c r="E121" t="s">
-        <v>388</v>
+        <v>334</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>423</v>
+        <v>115</v>
       </c>
       <c r="B122" t="s">
-        <v>342</v>
-      </c>
-      <c r="C122" t="s">
-        <v>203</v>
+        <v>335</v>
       </c>
       <c r="E122" t="s">
-        <v>389</v>
+        <v>336</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B123" t="s">
-        <v>221</v>
-      </c>
-      <c r="E123" t="s">
-        <v>343</v>
+        <v>337</v>
+      </c>
+      <c r="C123" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B124" t="s">
-        <v>310</v>
-      </c>
-      <c r="E124" t="s">
-        <v>390</v>
+        <v>339</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B125" t="s">
-        <v>305</v>
+        <v>226</v>
+      </c>
+      <c r="C125" t="s">
+        <v>202</v>
       </c>
       <c r="E125" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>122</v>
+        <v>420</v>
       </c>
       <c r="B126" t="s">
-        <v>344</v>
+        <v>340</v>
+      </c>
+      <c r="C126" t="s">
+        <v>202</v>
       </c>
       <c r="E126" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B127" t="s">
-        <v>345</v>
+        <v>220</v>
       </c>
       <c r="E127" t="s">
-        <v>392</v>
+        <v>341</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B128" t="s">
-        <v>346</v>
+        <v>308</v>
       </c>
       <c r="E128" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B129" t="s">
-        <v>347</v>
+        <v>303</v>
       </c>
       <c r="E129" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B130" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="E130" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B131" t="s">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="E131" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B132" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="E132" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B133" t="s">
-        <v>312</v>
+        <v>345</v>
       </c>
       <c r="E133" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B134" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E134" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B135" t="s">
-        <v>351</v>
+        <v>314</v>
       </c>
       <c r="E135" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B136" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="E136" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B137" t="s">
-        <v>353</v>
+        <v>310</v>
       </c>
       <c r="E137" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>417</v>
+        <v>130</v>
       </c>
       <c r="B138" t="s">
-        <v>418</v>
+        <v>348</v>
       </c>
       <c r="E138" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B139" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="E139" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B140" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="E140" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B141" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="E141" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>137</v>
+        <v>414</v>
       </c>
       <c r="B142" t="s">
-        <v>357</v>
+        <v>415</v>
       </c>
       <c r="E142" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>421</v>
+        <v>134</v>
       </c>
       <c r="B143" t="s">
-        <v>422</v>
+        <v>352</v>
       </c>
       <c r="E143" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B144" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="E144" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B145" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="E145" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B146" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="E146" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>141</v>
+        <v>418</v>
       </c>
       <c r="B147" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="E147" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B148" t="s">
-        <v>415</v>
+        <v>356</v>
       </c>
       <c r="E148" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B149" t="s">
-        <v>416</v>
+        <v>357</v>
       </c>
       <c r="E149" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B150" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E150" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B151" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E151" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B152" t="s">
-        <v>364</v>
+        <v>412</v>
       </c>
       <c r="E152" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B153" t="s">
-        <v>365</v>
+        <v>413</v>
       </c>
       <c r="E153" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>148</v>
-      </c>
-      <c r="C154" t="s">
-        <v>203</v>
+        <v>144</v>
+      </c>
+      <c r="B154" t="s">
+        <v>360</v>
       </c>
       <c r="E154" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B155" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="E155" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B156" t="s">
-        <v>367</v>
+        <v>421</v>
       </c>
       <c r="E156" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>151</v>
-      </c>
-      <c r="C157" t="s">
-        <v>203</v>
+        <v>439</v>
+      </c>
+      <c r="B157" t="s">
+        <v>421</v>
       </c>
       <c r="E157" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B158" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="E158" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C159" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E159" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="B160" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
       <c r="E160" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>155</v>
-      </c>
-      <c r="C161" t="s">
-        <v>203</v>
+        <v>150</v>
+      </c>
+      <c r="B161" t="s">
+        <v>364</v>
       </c>
       <c r="E161" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>156</v>
-      </c>
-      <c r="B162" t="s">
-        <v>370</v>
+        <v>151</v>
+      </c>
+      <c r="C162" t="s">
+        <v>202</v>
       </c>
       <c r="E162" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>157</v>
-      </c>
-      <c r="C163" t="s">
-        <v>203</v>
+        <v>152</v>
+      </c>
+      <c r="B163" t="s">
+        <v>365</v>
       </c>
       <c r="E163" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>158</v>
-      </c>
-      <c r="B164" t="s">
-        <v>371</v>
+        <v>153</v>
+      </c>
+      <c r="C164" t="s">
+        <v>202</v>
       </c>
       <c r="E164" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>159</v>
-      </c>
-      <c r="C165" t="s">
-        <v>203</v>
+        <v>154</v>
+      </c>
+      <c r="B165" t="s">
+        <v>366</v>
       </c>
       <c r="E165" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>160</v>
-      </c>
-      <c r="B166" t="s">
-        <v>372</v>
+        <v>155</v>
+      </c>
+      <c r="C166" t="s">
+        <v>202</v>
       </c>
       <c r="E166" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>161</v>
-      </c>
-      <c r="C167" t="s">
-        <v>203</v>
+        <v>156</v>
+      </c>
+      <c r="B167" t="s">
+        <v>367</v>
       </c>
       <c r="E167" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>162</v>
-      </c>
-      <c r="B168" t="s">
-        <v>373</v>
+        <v>157</v>
+      </c>
+      <c r="C168" t="s">
+        <v>202</v>
       </c>
       <c r="E168" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>163</v>
-      </c>
-      <c r="C169" t="s">
-        <v>203</v>
+        <v>158</v>
+      </c>
+      <c r="B169" t="s">
+        <v>368</v>
       </c>
       <c r="E169" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C170" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E170" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B171" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="E171" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C172" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E172" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B173" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="E173" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C174" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E174" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>420</v>
-      </c>
-      <c r="B175" t="s">
-        <v>419</v>
+        <v>164</v>
+      </c>
+      <c r="C175" t="s">
+        <v>202</v>
       </c>
       <c r="E175" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>169</v>
-      </c>
-      <c r="C176" t="s">
-        <v>203</v>
+        <v>165</v>
+      </c>
+      <c r="B176" t="s">
+        <v>371</v>
       </c>
       <c r="E176" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>170</v>
-      </c>
-      <c r="B177" t="s">
-        <v>376</v>
+        <v>166</v>
+      </c>
+      <c r="C177" t="s">
+        <v>202</v>
       </c>
       <c r="E177" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>171</v>
-      </c>
-      <c r="C178" t="s">
-        <v>203</v>
+        <v>167</v>
+      </c>
+      <c r="B178" t="s">
+        <v>372</v>
       </c>
       <c r="E178" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>172</v>
-      </c>
-      <c r="B179" t="s">
-        <v>377</v>
+        <v>168</v>
+      </c>
+      <c r="C179" t="s">
+        <v>202</v>
       </c>
       <c r="E179" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>173</v>
-      </c>
-      <c r="C180" t="s">
-        <v>203</v>
+        <v>417</v>
+      </c>
+      <c r="B180" t="s">
+        <v>416</v>
       </c>
       <c r="E180" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>174</v>
-      </c>
-      <c r="B181" t="s">
-        <v>378</v>
+        <v>169</v>
+      </c>
+      <c r="C181" t="s">
+        <v>202</v>
       </c>
       <c r="E181" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>175</v>
-      </c>
-      <c r="C182" t="s">
-        <v>203</v>
+        <v>170</v>
+      </c>
+      <c r="B182" t="s">
+        <v>373</v>
       </c>
       <c r="E182" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>176</v>
-      </c>
-      <c r="B183" t="s">
-        <v>379</v>
+        <v>171</v>
+      </c>
+      <c r="C183" t="s">
+        <v>202</v>
       </c>
       <c r="E183" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>177</v>
-      </c>
-      <c r="C184" t="s">
-        <v>203</v>
+        <v>172</v>
+      </c>
+      <c r="B184" t="s">
+        <v>374</v>
       </c>
       <c r="E184" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>178</v>
-      </c>
-      <c r="B185" t="s">
-        <v>380</v>
+        <v>173</v>
+      </c>
+      <c r="C185" t="s">
+        <v>202</v>
       </c>
       <c r="E185" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>179</v>
-      </c>
-      <c r="C186" t="s">
-        <v>203</v>
+        <v>174</v>
+      </c>
+      <c r="B186" t="s">
+        <v>375</v>
       </c>
       <c r="E186" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>180</v>
-      </c>
-      <c r="B187" t="s">
-        <v>381</v>
+        <v>175</v>
+      </c>
+      <c r="C187" t="s">
+        <v>202</v>
       </c>
       <c r="E187" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>181</v>
-      </c>
-      <c r="C188" t="s">
-        <v>203</v>
+        <v>176</v>
+      </c>
+      <c r="B188" t="s">
+        <v>376</v>
       </c>
       <c r="E188" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>182</v>
-      </c>
-      <c r="B189" t="s">
-        <v>382</v>
+        <v>177</v>
+      </c>
+      <c r="C189" t="s">
+        <v>202</v>
       </c>
       <c r="E189" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>183</v>
-      </c>
-      <c r="C190" t="s">
-        <v>203</v>
+        <v>178</v>
+      </c>
+      <c r="B190" t="s">
+        <v>377</v>
       </c>
       <c r="E190" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>184</v>
-      </c>
-      <c r="B191" t="s">
-        <v>383</v>
+        <v>179</v>
+      </c>
+      <c r="C191" t="s">
+        <v>202</v>
       </c>
       <c r="E191" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>185</v>
-      </c>
-      <c r="C192" t="s">
-        <v>203</v>
+        <v>180</v>
+      </c>
+      <c r="B192" t="s">
+        <v>378</v>
       </c>
       <c r="E192" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>186</v>
-      </c>
-      <c r="B193" t="s">
-        <v>384</v>
+        <v>181</v>
+      </c>
+      <c r="C193" t="s">
+        <v>202</v>
       </c>
       <c r="E193" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="B194" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="E194" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>188</v>
-      </c>
-      <c r="B195" t="s">
-        <v>386</v>
+        <v>183</v>
+      </c>
+      <c r="C195" t="s">
+        <v>202</v>
       </c>
       <c r="E195" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B196" t="s">
-        <v>410</v>
+        <v>380</v>
+      </c>
+      <c r="E196" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>190</v>
-      </c>
-      <c r="B197" t="s">
-        <v>411</v>
+        <v>185</v>
+      </c>
+      <c r="C197" t="s">
+        <v>202</v>
+      </c>
+      <c r="E197" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
+        <v>186</v>
+      </c>
+      <c r="B198" t="s">
+        <v>381</v>
+      </c>
+      <c r="E198" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>187</v>
+      </c>
+      <c r="B199" t="s">
+        <v>382</v>
+      </c>
+      <c r="E199" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>188</v>
+      </c>
+      <c r="B200" t="s">
+        <v>383</v>
+      </c>
+      <c r="E200" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>189</v>
+      </c>
+      <c r="B201" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>190</v>
+      </c>
+      <c r="B202" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
         <v>191</v>
       </c>
-      <c r="B198" t="s">
-        <v>387</v>
+      <c r="B203" t="s">
+        <v>384</v>
       </c>
     </row>
   </sheetData>
